--- a/artfynd/A 62816-2025 artfynd.xlsx
+++ b/artfynd/A 62816-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY93"/>
+  <dimension ref="A1:AY109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131167872</v>
+        <v>131167858</v>
       </c>
       <c r="B2" t="n">
-        <v>79017</v>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467563</v>
+        <v>467647</v>
       </c>
       <c r="R2" t="n">
-        <v>6797817</v>
+        <v>6797362</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,14 +782,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131167960</v>
+        <v>131167874</v>
       </c>
       <c r="B3" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467659</v>
+        <v>467567</v>
       </c>
       <c r="R3" t="n">
-        <v>6797458</v>
+        <v>6797649</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,14 +889,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131167899</v>
+        <v>131167889</v>
       </c>
       <c r="B4" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467639</v>
+        <v>467646</v>
       </c>
       <c r="R4" t="n">
-        <v>6797349</v>
+        <v>6797222</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,32 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131167871</v>
+        <v>131167890</v>
       </c>
       <c r="B5" t="n">
-        <v>78272</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467653</v>
+        <v>467641</v>
       </c>
       <c r="R5" t="n">
-        <v>6797353</v>
+        <v>6797236</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,50 +1103,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131167979</v>
+        <v>131167891</v>
       </c>
       <c r="B6" t="n">
-        <v>57898</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Näckånapp, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467642</v>
+        <v>467651</v>
       </c>
       <c r="R6" t="n">
-        <v>6797363</v>
+        <v>6797250</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,14 +1210,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131167962</v>
+        <v>131167892</v>
       </c>
       <c r="B7" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467677</v>
+        <v>467652</v>
       </c>
       <c r="R7" t="n">
-        <v>6797409</v>
+        <v>6797268</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,50 +1317,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131167862</v>
+        <v>131167893</v>
       </c>
       <c r="B8" t="n">
-        <v>57895</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Näckånapp, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>467561</v>
+        <v>467639</v>
       </c>
       <c r="R8" t="n">
-        <v>6797758</v>
+        <v>6797293</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,14 +1424,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131167902</v>
+        <v>131167894</v>
       </c>
       <c r="B9" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1469,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>467628</v>
+        <v>467619</v>
       </c>
       <c r="R9" t="n">
-        <v>6797384</v>
+        <v>6797306</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,14 +1531,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131167889</v>
+        <v>131167895</v>
       </c>
       <c r="B10" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1576,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>467646</v>
+        <v>467620</v>
       </c>
       <c r="R10" t="n">
-        <v>6797222</v>
+        <v>6797311</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,14 +1638,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131167933</v>
+        <v>131167896</v>
       </c>
       <c r="B11" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1683,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467545</v>
+        <v>467611</v>
       </c>
       <c r="R11" t="n">
-        <v>6797915</v>
+        <v>6797325</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,14 +1745,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131167922</v>
+        <v>131167897</v>
       </c>
       <c r="B12" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1790,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467590</v>
+        <v>467604</v>
       </c>
       <c r="R12" t="n">
-        <v>6797817</v>
+        <v>6797348</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,14 +1852,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131167920</v>
+        <v>131167898</v>
       </c>
       <c r="B13" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1897,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467605</v>
+        <v>467623</v>
       </c>
       <c r="R13" t="n">
-        <v>6797771</v>
+        <v>6797349</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,14 +1959,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131167971</v>
+        <v>131167899</v>
       </c>
       <c r="B14" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2004,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467689</v>
+        <v>467639</v>
       </c>
       <c r="R14" t="n">
-        <v>6797293</v>
+        <v>6797349</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2039,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2049,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2076,14 +2066,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131167915</v>
+        <v>131167900</v>
       </c>
       <c r="B15" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2111,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467623</v>
+        <v>467647</v>
       </c>
       <c r="R15" t="n">
-        <v>6797612</v>
+        <v>6797353</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2146,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2156,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2183,30 +2173,34 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131167875</v>
+        <v>131167901</v>
       </c>
       <c r="B16" t="n">
-        <v>91848</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2214,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467596</v>
+        <v>467647</v>
       </c>
       <c r="R16" t="n">
-        <v>6797790</v>
+        <v>6797361</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2249,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2259,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2286,14 +2280,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131167937</v>
+        <v>131167902</v>
       </c>
       <c r="B17" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2321,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467549</v>
+        <v>467628</v>
       </c>
       <c r="R17" t="n">
-        <v>6797866</v>
+        <v>6797384</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2356,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2366,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2393,14 +2387,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131167917</v>
+        <v>131167903</v>
       </c>
       <c r="B18" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2428,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467617</v>
+        <v>467604</v>
       </c>
       <c r="R18" t="n">
-        <v>6797685</v>
+        <v>6797394</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2463,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2473,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2500,14 +2494,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131167923</v>
+        <v>131167904</v>
       </c>
       <c r="B19" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2535,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>467579</v>
+        <v>467602</v>
       </c>
       <c r="R19" t="n">
-        <v>6797836</v>
+        <v>6797434</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2570,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2580,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2607,32 +2601,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131167856</v>
+        <v>131167905</v>
       </c>
       <c r="B20" t="n">
-        <v>83240</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2642,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>467561</v>
+        <v>467584</v>
       </c>
       <c r="R20" t="n">
-        <v>6797709</v>
+        <v>6797447</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2677,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2687,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2714,14 +2708,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131167890</v>
+        <v>131167906</v>
       </c>
       <c r="B21" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2749,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467641</v>
+        <v>467599</v>
       </c>
       <c r="R21" t="n">
-        <v>6797236</v>
+        <v>6797480</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2784,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2794,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2821,50 +2815,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131167976</v>
+        <v>131167907</v>
       </c>
       <c r="B22" t="n">
-        <v>57898</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Näckånapp, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>467639</v>
+        <v>467592</v>
       </c>
       <c r="R22" t="n">
-        <v>6797349</v>
+        <v>6797489</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2896,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2906,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2933,50 +2922,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131167984</v>
+        <v>131167908</v>
       </c>
       <c r="B23" t="n">
-        <v>57898</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Näckånapp, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>467672</v>
+        <v>467579</v>
       </c>
       <c r="R23" t="n">
-        <v>6797328</v>
+        <v>6797494</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3008,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3018,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3045,14 +3029,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131167955</v>
+        <v>131167909</v>
       </c>
       <c r="B24" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3080,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>467647</v>
+        <v>467588</v>
       </c>
       <c r="R24" t="n">
-        <v>6797568</v>
+        <v>6797507</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3115,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3125,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3152,14 +3136,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131167874</v>
+        <v>131167910</v>
       </c>
       <c r="B25" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3187,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>467567</v>
+        <v>467599</v>
       </c>
       <c r="R25" t="n">
-        <v>6797649</v>
+        <v>6797517</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3222,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3232,7 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3259,14 +3243,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131167953</v>
+        <v>131167911</v>
       </c>
       <c r="B26" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3294,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>467593</v>
+        <v>467602</v>
       </c>
       <c r="R26" t="n">
-        <v>6797597</v>
+        <v>6797531</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3329,7 +3313,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3339,7 +3323,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3366,14 +3350,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131167940</v>
+        <v>131167912</v>
       </c>
       <c r="B27" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3401,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467552</v>
+        <v>467598</v>
       </c>
       <c r="R27" t="n">
-        <v>6797804</v>
+        <v>6797550</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3436,7 +3420,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3446,7 +3430,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3473,14 +3457,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131167898</v>
+        <v>131167913</v>
       </c>
       <c r="B28" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3508,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>467623</v>
+        <v>467611</v>
       </c>
       <c r="R28" t="n">
-        <v>6797349</v>
+        <v>6797569</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3543,7 +3527,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3553,7 +3537,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3580,32 +3564,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131167870</v>
+        <v>131167914</v>
       </c>
       <c r="B29" t="n">
-        <v>80401</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3615,10 +3599,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>467659</v>
+        <v>467622</v>
       </c>
       <c r="R29" t="n">
-        <v>6797460</v>
+        <v>6797592</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3650,7 +3634,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3660,7 +3644,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3671,21 +3655,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3702,14 +3671,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131167936</v>
+        <v>131167915</v>
       </c>
       <c r="B30" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3737,10 +3706,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>467544</v>
+        <v>467623</v>
       </c>
       <c r="R30" t="n">
-        <v>6797873</v>
+        <v>6797612</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3772,7 +3741,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3782,7 +3751,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3809,14 +3778,14 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131167926</v>
+        <v>131167916</v>
       </c>
       <c r="B31" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -3844,10 +3813,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467598</v>
+        <v>467623</v>
       </c>
       <c r="R31" t="n">
-        <v>6797908</v>
+        <v>6797638</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3879,7 +3848,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3889,7 +3858,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3916,50 +3885,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131167981</v>
+        <v>131167917</v>
       </c>
       <c r="B32" t="n">
-        <v>57898</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Näckånapp, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467577</v>
+        <v>467617</v>
       </c>
       <c r="R32" t="n">
-        <v>6797814</v>
+        <v>6797685</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3991,7 +3955,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4001,7 +3965,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4028,14 +3992,14 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131167967</v>
+        <v>131167918</v>
       </c>
       <c r="B33" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -4063,10 +4027,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467672</v>
+        <v>467591</v>
       </c>
       <c r="R33" t="n">
-        <v>6797328</v>
+        <v>6797763</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4098,7 +4062,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4108,7 +4072,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4135,14 +4099,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131167966</v>
+        <v>131167919</v>
       </c>
       <c r="B34" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4170,10 +4134,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>467699</v>
+        <v>467592</v>
       </c>
       <c r="R34" t="n">
-        <v>6797334</v>
+        <v>6797765</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4205,7 +4169,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4215,7 +4179,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4242,14 +4206,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131167958</v>
+        <v>131167920</v>
       </c>
       <c r="B35" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4277,10 +4241,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>467667</v>
+        <v>467605</v>
       </c>
       <c r="R35" t="n">
-        <v>6797503</v>
+        <v>6797771</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4312,7 +4276,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4322,7 +4286,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4349,14 +4313,14 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131167934</v>
+        <v>131167921</v>
       </c>
       <c r="B36" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4384,10 +4348,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>467517</v>
+        <v>467590</v>
       </c>
       <c r="R36" t="n">
-        <v>6797908</v>
+        <v>6797795</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4419,7 +4383,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4429,7 +4393,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4456,50 +4420,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131167978</v>
+        <v>131167922</v>
       </c>
       <c r="B37" t="n">
-        <v>57898</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Näckånapp, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>467649</v>
+        <v>467590</v>
       </c>
       <c r="R37" t="n">
-        <v>6797351</v>
+        <v>6797817</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4531,7 +4490,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4541,7 +4500,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4568,14 +4527,14 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131167913</v>
+        <v>131167923</v>
       </c>
       <c r="B38" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4603,10 +4562,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>467611</v>
+        <v>467579</v>
       </c>
       <c r="R38" t="n">
-        <v>6797569</v>
+        <v>6797836</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4638,7 +4597,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4648,7 +4607,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4675,14 +4634,14 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131167919</v>
+        <v>131167924</v>
       </c>
       <c r="B39" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -4710,10 +4669,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467592</v>
+        <v>467578</v>
       </c>
       <c r="R39" t="n">
-        <v>6797765</v>
+        <v>6797876</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4745,7 +4704,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4755,7 +4714,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4782,14 +4741,14 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131167961</v>
+        <v>131167936</v>
       </c>
       <c r="B40" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -4817,10 +4776,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467662</v>
+        <v>467544</v>
       </c>
       <c r="R40" t="n">
-        <v>6797441</v>
+        <v>6797873</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4852,7 +4811,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4862,7 +4821,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4889,14 +4848,14 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131167931</v>
+        <v>131167937</v>
       </c>
       <c r="B41" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -4924,10 +4883,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467558</v>
+        <v>467549</v>
       </c>
       <c r="R41" t="n">
-        <v>6797922</v>
+        <v>6797866</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4959,7 +4918,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4969,7 +4928,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4996,14 +4955,14 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131167952</v>
+        <v>131167938</v>
       </c>
       <c r="B42" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -5031,10 +4990,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467574</v>
+        <v>467578</v>
       </c>
       <c r="R42" t="n">
-        <v>6797625</v>
+        <v>6797832</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5066,7 +5025,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5076,7 +5035,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5103,14 +5062,14 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131167929</v>
+        <v>131167939</v>
       </c>
       <c r="B43" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -5138,10 +5097,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>467511</v>
+        <v>467562</v>
       </c>
       <c r="R43" t="n">
-        <v>6798010</v>
+        <v>6797811</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5173,7 +5132,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5183,7 +5142,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5210,14 +5169,14 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131167901</v>
+        <v>131167940</v>
       </c>
       <c r="B44" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -5245,10 +5204,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>467647</v>
+        <v>467552</v>
       </c>
       <c r="R44" t="n">
-        <v>6797361</v>
+        <v>6797804</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5280,7 +5239,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5290,7 +5249,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5317,14 +5276,14 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131167943</v>
+        <v>131167941</v>
       </c>
       <c r="B45" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -5352,10 +5311,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>467577</v>
+        <v>467556</v>
       </c>
       <c r="R45" t="n">
-        <v>6797766</v>
+        <v>6797789</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5424,32 +5383,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131167876</v>
+        <v>131167942</v>
       </c>
       <c r="B46" t="n">
-        <v>92247</v>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6040186</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5459,10 +5418,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>467710</v>
+        <v>467567</v>
       </c>
       <c r="R46" t="n">
-        <v>6797303</v>
+        <v>6797786</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5494,7 +5453,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5504,7 +5463,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5513,7 +5472,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5532,14 +5490,14 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131167891</v>
+        <v>131167943</v>
       </c>
       <c r="B47" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -5567,10 +5525,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>467651</v>
+        <v>467577</v>
       </c>
       <c r="R47" t="n">
-        <v>6797250</v>
+        <v>6797766</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5602,7 +5560,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5612,7 +5570,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5639,14 +5597,14 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131167954</v>
+        <v>131167944</v>
       </c>
       <c r="B48" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -5674,10 +5632,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>467633</v>
+        <v>467571</v>
       </c>
       <c r="R48" t="n">
-        <v>6797570</v>
+        <v>6797758</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5709,7 +5667,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5719,7 +5677,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5746,14 +5704,14 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131167942</v>
+        <v>131167945</v>
       </c>
       <c r="B49" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -5781,10 +5739,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>467567</v>
+        <v>467551</v>
       </c>
       <c r="R49" t="n">
-        <v>6797786</v>
+        <v>6797761</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5816,7 +5774,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5826,7 +5784,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5853,14 +5811,14 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131167893</v>
+        <v>131167946</v>
       </c>
       <c r="B50" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -5888,10 +5846,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>467639</v>
+        <v>467569</v>
       </c>
       <c r="R50" t="n">
-        <v>6797293</v>
+        <v>6797726</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5923,7 +5881,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5933,7 +5891,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5960,50 +5918,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131167867</v>
+        <v>131167947</v>
       </c>
       <c r="B51" t="n">
-        <v>57898</v>
+        <v>79327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Näckånapp, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>467703</v>
+        <v>467565</v>
       </c>
       <c r="R51" t="n">
-        <v>6797331</v>
+        <v>6797695</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6035,7 +5988,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6045,12 +5998,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>17:17</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6077,50 +6025,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131167860</v>
+        <v>131167948</v>
       </c>
       <c r="B52" t="n">
-        <v>4773</v>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Näckånapp, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>467601</v>
+        <v>467562</v>
       </c>
       <c r="R52" t="n">
-        <v>6797468</v>
+        <v>6797682</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6152,7 +6095,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6162,7 +6105,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6189,14 +6132,14 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131167938</v>
+        <v>131167949</v>
       </c>
       <c r="B53" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -6224,10 +6167,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>467578</v>
+        <v>467565</v>
       </c>
       <c r="R53" t="n">
-        <v>6797832</v>
+        <v>6797674</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6259,7 +6202,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6269,7 +6212,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6296,14 +6239,14 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131167963</v>
+        <v>131167950</v>
       </c>
       <c r="B54" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -6331,10 +6274,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>467679</v>
+        <v>467569</v>
       </c>
       <c r="R54" t="n">
-        <v>6797386</v>
+        <v>6797667</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6366,7 +6309,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6376,7 +6319,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6403,14 +6346,14 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131167932</v>
+        <v>131167951</v>
       </c>
       <c r="B55" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -6438,10 +6381,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>467553</v>
+        <v>467571</v>
       </c>
       <c r="R55" t="n">
-        <v>6797919</v>
+        <v>6797635</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6473,7 +6416,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6483,7 +6426,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6510,14 +6453,14 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131167916</v>
+        <v>131167952</v>
       </c>
       <c r="B56" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -6545,10 +6488,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>467623</v>
+        <v>467574</v>
       </c>
       <c r="R56" t="n">
-        <v>6797638</v>
+        <v>6797625</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6580,7 +6523,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6590,7 +6533,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6617,14 +6560,14 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131167918</v>
+        <v>131167953</v>
       </c>
       <c r="B57" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -6652,10 +6595,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>467591</v>
+        <v>467593</v>
       </c>
       <c r="R57" t="n">
-        <v>6797763</v>
+        <v>6797597</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6687,7 +6630,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6697,7 +6640,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6724,14 +6667,14 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131167921</v>
+        <v>131167954</v>
       </c>
       <c r="B58" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -6759,10 +6702,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>467590</v>
+        <v>467633</v>
       </c>
       <c r="R58" t="n">
-        <v>6797795</v>
+        <v>6797570</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6794,7 +6737,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6804,7 +6747,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6831,32 +6774,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131167857</v>
+        <v>131167955</v>
       </c>
       <c r="B59" t="n">
-        <v>83240</v>
+        <v>79327</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6866,10 +6809,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>467564</v>
+        <v>467647</v>
       </c>
       <c r="R59" t="n">
-        <v>6797696</v>
+        <v>6797568</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6901,7 +6844,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6911,7 +6854,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6938,32 +6881,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131167983</v>
+        <v>131167956</v>
       </c>
       <c r="B60" t="n">
-        <v>78663</v>
+        <v>79327</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6973,10 +6916,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>467644</v>
+        <v>467656</v>
       </c>
       <c r="R60" t="n">
-        <v>6797577</v>
+        <v>6797536</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7008,7 +6951,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7018,7 +6961,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7045,14 +6988,14 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131167947</v>
+        <v>131167957</v>
       </c>
       <c r="B61" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -7080,10 +7023,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>467565</v>
+        <v>467666</v>
       </c>
       <c r="R61" t="n">
-        <v>6797695</v>
+        <v>6797520</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7115,7 +7058,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7125,7 +7068,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7152,14 +7095,14 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131167912</v>
+        <v>131167958</v>
       </c>
       <c r="B62" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -7187,10 +7130,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>467598</v>
+        <v>467667</v>
       </c>
       <c r="R62" t="n">
-        <v>6797550</v>
+        <v>6797503</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7222,7 +7165,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7232,7 +7175,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7259,14 +7202,14 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131167925</v>
+        <v>131167959</v>
       </c>
       <c r="B63" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -7294,10 +7237,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>467583</v>
+        <v>467665</v>
       </c>
       <c r="R63" t="n">
-        <v>6797900</v>
+        <v>6797492</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7329,7 +7272,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7339,7 +7282,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7366,50 +7309,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131167982</v>
+        <v>131167960</v>
       </c>
       <c r="B64" t="n">
-        <v>57898</v>
+        <v>79327</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Näckånapp, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>467658</v>
+        <v>467659</v>
       </c>
       <c r="R64" t="n">
-        <v>6797466</v>
+        <v>6797458</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7441,7 +7379,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7451,7 +7389,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7478,14 +7416,14 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131167911</v>
+        <v>131167961</v>
       </c>
       <c r="B65" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -7513,10 +7451,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>467602</v>
+        <v>467662</v>
       </c>
       <c r="R65" t="n">
-        <v>6797531</v>
+        <v>6797441</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7548,7 +7486,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7558,7 +7496,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7585,14 +7523,14 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131167959</v>
+        <v>131167962</v>
       </c>
       <c r="B66" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -7620,10 +7558,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>467665</v>
+        <v>467677</v>
       </c>
       <c r="R66" t="n">
-        <v>6797492</v>
+        <v>6797409</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7655,7 +7593,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7665,7 +7603,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7692,14 +7630,14 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131167968</v>
+        <v>131167963</v>
       </c>
       <c r="B67" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -7727,10 +7665,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>467656</v>
+        <v>467679</v>
       </c>
       <c r="R67" t="n">
-        <v>6797345</v>
+        <v>6797386</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7762,7 +7700,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7772,7 +7710,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7799,14 +7737,14 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131167927</v>
+        <v>131167964</v>
       </c>
       <c r="B68" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -7834,10 +7772,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>467608</v>
+        <v>467685</v>
       </c>
       <c r="R68" t="n">
-        <v>6797937</v>
+        <v>6797361</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7869,7 +7807,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7879,7 +7817,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7906,14 +7844,14 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131167946</v>
+        <v>131167965</v>
       </c>
       <c r="B69" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -7941,10 +7879,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>467569</v>
+        <v>467694</v>
       </c>
       <c r="R69" t="n">
-        <v>6797726</v>
+        <v>6797345</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7976,7 +7914,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7986,7 +7924,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8013,50 +7951,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131167975</v>
+        <v>131167966</v>
       </c>
       <c r="B70" t="n">
-        <v>57898</v>
+        <v>79327</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Näckånapp, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>467592</v>
+        <v>467699</v>
       </c>
       <c r="R70" t="n">
-        <v>6797810</v>
+        <v>6797334</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8088,7 +8021,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8098,14 +8031,14 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG70" t="b">
         <v>0</v>
@@ -8125,14 +8058,14 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131167951</v>
+        <v>131167967</v>
       </c>
       <c r="B71" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -8160,10 +8093,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>467571</v>
+        <v>467672</v>
       </c>
       <c r="R71" t="n">
-        <v>6797635</v>
+        <v>6797328</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8195,7 +8128,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8205,7 +8138,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8232,14 +8165,14 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131167900</v>
+        <v>131167968</v>
       </c>
       <c r="B72" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -8267,10 +8200,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>467647</v>
+        <v>467656</v>
       </c>
       <c r="R72" t="n">
-        <v>6797353</v>
+        <v>6797345</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8302,7 +8235,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8312,7 +8245,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8339,14 +8272,14 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131167950</v>
+        <v>131167969</v>
       </c>
       <c r="B73" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -8374,10 +8307,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>467569</v>
+        <v>467656</v>
       </c>
       <c r="R73" t="n">
-        <v>6797667</v>
+        <v>6797324</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8409,7 +8342,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8419,7 +8352,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8446,14 +8379,14 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131167904</v>
+        <v>131167970</v>
       </c>
       <c r="B74" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -8481,10 +8414,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>467602</v>
+        <v>467665</v>
       </c>
       <c r="R74" t="n">
-        <v>6797434</v>
+        <v>6797301</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8516,7 +8449,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8526,7 +8459,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8553,14 +8486,14 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131167965</v>
+        <v>131167971</v>
       </c>
       <c r="B75" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -8588,10 +8521,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>467694</v>
+        <v>467689</v>
       </c>
       <c r="R75" t="n">
-        <v>6797345</v>
+        <v>6797293</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8623,7 +8556,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8633,7 +8566,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8660,14 +8593,14 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131167914</v>
+        <v>131167972</v>
       </c>
       <c r="B76" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -8695,10 +8628,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>467622</v>
+        <v>467666</v>
       </c>
       <c r="R76" t="n">
-        <v>6797592</v>
+        <v>6797209</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8730,7 +8663,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8740,7 +8673,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8767,32 +8700,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131167964</v>
+        <v>131167868</v>
       </c>
       <c r="B77" t="n">
-        <v>79260</v>
+        <v>79351</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8802,10 +8735,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>467685</v>
+        <v>467662</v>
       </c>
       <c r="R77" t="n">
-        <v>6797361</v>
+        <v>6797514</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8837,7 +8770,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8847,7 +8780,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8874,10 +8807,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131167970</v>
+        <v>131167983</v>
       </c>
       <c r="B78" t="n">
-        <v>79260</v>
+        <v>78730</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8885,21 +8818,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8909,10 +8842,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>467665</v>
+        <v>467644</v>
       </c>
       <c r="R78" t="n">
-        <v>6797301</v>
+        <v>6797577</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8944,7 +8877,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8954,7 +8887,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8981,10 +8914,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131167924</v>
+        <v>131167856</v>
       </c>
       <c r="B79" t="n">
-        <v>79260</v>
+        <v>83307</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8992,21 +8925,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9016,10 +8949,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>467578</v>
+        <v>467561</v>
       </c>
       <c r="R79" t="n">
-        <v>6797876</v>
+        <v>6797709</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9051,7 +8984,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9061,7 +8994,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9088,10 +9021,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131167944</v>
+        <v>131167857</v>
       </c>
       <c r="B80" t="n">
-        <v>79260</v>
+        <v>83307</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9099,21 +9032,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9123,10 +9056,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>467571</v>
+        <v>467564</v>
       </c>
       <c r="R80" t="n">
-        <v>6797758</v>
+        <v>6797696</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9158,7 +9091,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9168,7 +9101,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9195,10 +9128,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131167907</v>
+        <v>131167872</v>
       </c>
       <c r="B81" t="n">
-        <v>79260</v>
+        <v>79084</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9206,21 +9139,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9230,10 +9163,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>467592</v>
+        <v>467563</v>
       </c>
       <c r="R81" t="n">
-        <v>6797489</v>
+        <v>6797817</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9265,7 +9198,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9275,7 +9208,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9302,32 +9235,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131167945</v>
+        <v>131167870</v>
       </c>
       <c r="B82" t="n">
-        <v>79260</v>
+        <v>80468</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9337,10 +9270,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>467551</v>
+        <v>467659</v>
       </c>
       <c r="R82" t="n">
-        <v>6797761</v>
+        <v>6797460</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9372,7 +9305,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9382,7 +9315,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9393,6 +9326,21 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -9409,45 +9357,50 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131167892</v>
+        <v>131167862</v>
       </c>
       <c r="B83" t="n">
-        <v>79260</v>
+        <v>57950</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Näckånapp, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>467652</v>
+        <v>467561</v>
       </c>
       <c r="R83" t="n">
-        <v>6797268</v>
+        <v>6797758</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9479,7 +9432,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9489,7 +9442,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9516,10 +9469,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131167939</v>
+        <v>131167867</v>
       </c>
       <c r="B84" t="n">
-        <v>79260</v>
+        <v>57953</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9527,34 +9480,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Näckånapp, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>467562</v>
+        <v>467703</v>
       </c>
       <c r="R84" t="n">
-        <v>6797811</v>
+        <v>6797331</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9586,7 +9544,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9596,7 +9554,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9623,10 +9586,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131167906</v>
+        <v>131167974</v>
       </c>
       <c r="B85" t="n">
-        <v>79260</v>
+        <v>57953</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9634,34 +9597,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Näckånapp, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>467599</v>
+        <v>467610</v>
       </c>
       <c r="R85" t="n">
-        <v>6797480</v>
+        <v>6797348</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9693,7 +9661,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9703,14 +9671,14 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG85" t="b">
         <v>0</v>
@@ -9730,45 +9698,50 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131167858</v>
+        <v>131167975</v>
       </c>
       <c r="B86" t="n">
-        <v>91791</v>
+        <v>57953</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Näckånapp, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>467647</v>
+        <v>467592</v>
       </c>
       <c r="R86" t="n">
-        <v>6797362</v>
+        <v>6797810</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9800,7 +9773,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9810,14 +9783,14 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG86" t="b">
         <v>0</v>
@@ -9837,10 +9810,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131167910</v>
+        <v>131167976</v>
       </c>
       <c r="B87" t="n">
-        <v>79260</v>
+        <v>57953</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9848,34 +9821,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Näckånapp, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>467599</v>
+        <v>467639</v>
       </c>
       <c r="R87" t="n">
-        <v>6797517</v>
+        <v>6797349</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9907,7 +9885,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9917,7 +9895,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9944,10 +9922,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131167949</v>
+        <v>131167977</v>
       </c>
       <c r="B88" t="n">
-        <v>79260</v>
+        <v>57953</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9955,34 +9933,39 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Näckånapp, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>467565</v>
+        <v>467620</v>
       </c>
       <c r="R88" t="n">
-        <v>6797674</v>
+        <v>6797309</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10014,7 +9997,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10024,7 +10007,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10051,10 +10034,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131167941</v>
+        <v>131167978</v>
       </c>
       <c r="B89" t="n">
-        <v>79260</v>
+        <v>57953</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10062,34 +10045,39 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Näckånapp, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>467556</v>
+        <v>467649</v>
       </c>
       <c r="R89" t="n">
-        <v>6797789</v>
+        <v>6797351</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10121,7 +10109,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10131,7 +10119,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10158,10 +10146,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131167969</v>
+        <v>131167979</v>
       </c>
       <c r="B90" t="n">
-        <v>79260</v>
+        <v>57953</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10169,34 +10157,39 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Näckånapp, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>467656</v>
+        <v>467642</v>
       </c>
       <c r="R90" t="n">
-        <v>6797324</v>
+        <v>6797363</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10228,7 +10221,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10238,7 +10231,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10265,10 +10258,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131167935</v>
+        <v>131167980</v>
       </c>
       <c r="B91" t="n">
-        <v>79260</v>
+        <v>57953</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10276,34 +10269,39 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Näckånapp, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>467546</v>
+        <v>467584</v>
       </c>
       <c r="R91" t="n">
-        <v>6797891</v>
+        <v>6797493</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10335,7 +10333,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10345,7 +10343,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10372,10 +10370,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131167930</v>
+        <v>131167981</v>
       </c>
       <c r="B92" t="n">
-        <v>79260</v>
+        <v>57953</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10383,34 +10381,39 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Näckånapp, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>467562</v>
+        <v>467577</v>
       </c>
       <c r="R92" t="n">
-        <v>6797958</v>
+        <v>6797814</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10442,7 +10445,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10452,7 +10455,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10479,10 +10482,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131167948</v>
+        <v>131167982</v>
       </c>
       <c r="B93" t="n">
-        <v>79260</v>
+        <v>57953</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10490,34 +10493,39 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Näckånapp, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>467562</v>
+        <v>467658</v>
       </c>
       <c r="R93" t="n">
-        <v>6797682</v>
+        <v>6797466</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10549,7 +10557,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10559,7 +10567,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10583,6 +10591,1729 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>131167984</v>
+      </c>
+      <c r="B94" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Näckånapp, Dlr</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>467672</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6797328</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>131167860</v>
+      </c>
+      <c r="B95" t="n">
+        <v>4775</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Näckånapp, Dlr</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>467601</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6797468</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>131167871</v>
+      </c>
+      <c r="B96" t="n">
+        <v>78339</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Näckånapp, Dlr</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>467653</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6797353</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>131167861</v>
+      </c>
+      <c r="B97" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Näckånapp, Dlr</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>467576</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6797615</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>131167876</v>
+      </c>
+      <c r="B98" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Näckånapp, Dlr</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>467710</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6797303</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF98" t="inlineStr"/>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>131167925</v>
+      </c>
+      <c r="B99" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Näckånapp, Dlr</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>467583</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6797900</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>131167926</v>
+      </c>
+      <c r="B100" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Näckånapp, Dlr</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>467598</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6797908</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>131167927</v>
+      </c>
+      <c r="B101" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Näckånapp, Dlr</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>467608</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6797937</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>131167928</v>
+      </c>
+      <c r="B102" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Näckånapp, Dlr</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>467498</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6797934</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>131167929</v>
+      </c>
+      <c r="B103" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Näckånapp, Dlr</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>467511</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6798010</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>131167930</v>
+      </c>
+      <c r="B104" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Näckånapp, Dlr</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>467562</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6797958</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>131167931</v>
+      </c>
+      <c r="B105" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Näckånapp, Dlr</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>467558</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6797922</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>131167932</v>
+      </c>
+      <c r="B106" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Näckånapp, Dlr</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>467553</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6797919</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>131167933</v>
+      </c>
+      <c r="B107" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Näckånapp, Dlr</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>467545</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6797915</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>131167934</v>
+      </c>
+      <c r="B108" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Näckånapp, Dlr</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>467517</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6797908</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>131167935</v>
+      </c>
+      <c r="B109" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Näckånapp, Dlr</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>467546</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6797891</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62816-2025 artfynd.xlsx
+++ b/artfynd/A 62816-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY110"/>
+  <dimension ref="A1:AZ110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167858</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167874</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167889</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167890</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167891</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167892</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167893</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167894</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167895</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167896</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167897</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167898</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2128,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167899</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2170,6 +2240,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167900</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2277,6 +2352,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167901</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2384,6 +2464,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167902</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2491,6 +2576,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167903</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2598,6 +2688,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167904</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2705,6 +2800,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167905</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2812,6 +2912,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167906</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2919,6 +3024,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167907</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3026,6 +3136,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167908</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3133,6 +3248,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167909</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3240,6 +3360,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167910</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3347,6 +3472,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167911</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3454,6 +3584,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167912</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3561,6 +3696,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167913</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3668,6 +3808,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167914</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3775,6 +3920,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167915</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3882,6 +4032,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167916</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3989,6 +4144,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167917</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4096,6 +4256,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167918</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4203,6 +4368,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167919</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4310,6 +4480,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167920</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4417,6 +4592,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167921</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4524,6 +4704,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167922</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4631,6 +4816,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167923</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4738,6 +4928,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167924</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4845,6 +5040,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167925</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4952,6 +5152,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167926</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5059,6 +5264,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167927</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5166,6 +5376,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167928</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5273,6 +5488,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167929</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5380,6 +5600,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167930</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5487,6 +5712,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167931</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5594,6 +5824,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167932</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5701,6 +5936,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167933</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5808,6 +6048,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167934</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5915,6 +6160,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167935</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6022,6 +6272,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167936</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6129,6 +6384,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167937</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6236,6 +6496,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167938</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6343,6 +6608,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167939</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6450,6 +6720,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167940</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6557,6 +6832,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167941</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6664,6 +6944,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167942</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6771,6 +7056,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167943</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6878,6 +7168,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167944</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6985,6 +7280,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167945</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7092,6 +7392,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167946</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7199,6 +7504,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167947</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7306,6 +7616,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167948</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7413,6 +7728,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167949</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7520,6 +7840,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167950</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7627,6 +7952,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167951</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7734,6 +8064,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167952</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7841,6 +8176,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167953</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7948,6 +8288,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167954</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8055,6 +8400,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167955</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8162,6 +8512,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167956</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8269,6 +8624,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167957</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8376,6 +8736,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167958</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8483,6 +8848,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167959</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8590,6 +8960,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167960</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8697,6 +9072,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167961</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8804,6 +9184,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167962</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8911,6 +9296,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167963</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9018,6 +9408,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167964</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9125,6 +9520,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167965</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9232,6 +9632,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167966</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9339,6 +9744,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167967</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9446,6 +9856,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167968</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9553,6 +9968,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167969</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9660,6 +10080,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167970</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9767,6 +10192,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167971</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9874,6 +10304,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167972</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9971,6 +10406,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134955297</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10078,6 +10518,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167868</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10185,6 +10630,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167983</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10292,6 +10742,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167856</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10399,6 +10854,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167857</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10506,6 +10966,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167872</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10628,6 +11093,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167870</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10740,6 +11210,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167862</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10857,6 +11332,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167867</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10969,6 +11449,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167974</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11081,6 +11566,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167975</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11193,6 +11683,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167976</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11305,6 +11800,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167977</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11417,6 +11917,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167978</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11529,6 +12034,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167979</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11641,6 +12151,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167980</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11753,6 +12268,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167981</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11865,6 +12385,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167982</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11977,6 +12502,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167984</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12089,6 +12619,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167860</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12196,6 +12731,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167871</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12303,6 +12843,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167861</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12411,8 +12956,124 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131167876</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 62816-2025 artfynd.xlsx
+++ b/artfynd/A 62816-2025 artfynd.xlsx
@@ -10315,7 +10315,7 @@
         <v>134955297</v>
       </c>
       <c r="B88" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
